--- a/files/港岛-铜锣湾-宏丰台10号.xlsx
+++ b/files/港岛-铜锣湾-宏丰台10号.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏丰台10号 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -18,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -40,65 +39,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -109,42 +51,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -174,7 +80,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -187,42 +93,6 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -970,220 +840,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>宏丰台10号 - 宏丰台10号 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="5" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="6" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="7" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="8" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="9" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="5" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="10" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-      <c r="B3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="C3" s="12" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="D3" s="13" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="E3" s="14" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="10" t="inlineStr">
-        <is>
-          <t>6 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>3/F</t>
-        </is>
-      </c>
-      <c r="B6" s="15" t="inlineStr"/>
-      <c r="C6" s="15" t="inlineStr"/>
-      <c r="D6" s="15" t="inlineStr"/>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 205呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="F6" s="16" t="inlineStr">
-        <is>
-          <t>E | 249呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="G6" s="16" t="inlineStr">
-        <is>
-          <t>F | 172呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;2/F</t>
-        </is>
-      </c>
-      <c r="B7" s="15" t="inlineStr"/>
-      <c r="C7" s="15" t="inlineStr"/>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 730呎 (开放式)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="inlineStr"/>
-      <c r="F7" s="15" t="inlineStr"/>
-      <c r="G7" s="15" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>G&amp;1-3/F</t>
-        </is>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>A | 4398呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>B | 4178呎 (2房)
-暂无价格
-暂无呎价
-(待售)</t>
-        </is>
-      </c>
-      <c r="D8" s="15" t="inlineStr"/>
-      <c r="E8" s="15" t="inlineStr"/>
-      <c r="F8" s="15" t="inlineStr"/>
-      <c r="G8" s="15" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:G1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-铜锣湾-宏丰台10号.xlsx
+++ b/files/港岛-铜锣湾-宏丰台10号.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="宏丰台10号" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="18">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -39,8 +40,85 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -51,6 +129,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -80,7 +194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -93,6 +207,54 @@
     </xf>
     <xf numFmtId="3" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -840,4 +1002,220 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>宏丰台10号 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="7" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="8" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="9" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="10" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="11" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B3" s="13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C3" s="14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D3" s="15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E3" s="16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="18" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="18" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="18" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="18" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="18" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="18" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="G4" s="18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B5" s="19" t="inlineStr"/>
+      <c r="C5" s="19" t="inlineStr"/>
+      <c r="D5" s="19" t="inlineStr"/>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 205呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="F5" s="20" t="inlineStr">
+        <is>
+          <t>E | 249呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="G5" s="20" t="inlineStr">
+        <is>
+          <t>F | 172呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="18" t="inlineStr">
+        <is>
+          <t>G&amp;2</t>
+        </is>
+      </c>
+      <c r="B6" s="19" t="inlineStr"/>
+      <c r="C6" s="19" t="inlineStr"/>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 730呎 (开放式)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="inlineStr"/>
+      <c r="F6" s="19" t="inlineStr"/>
+      <c r="G6" s="19" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="18" t="inlineStr">
+        <is>
+          <t>G&amp;1-3</t>
+        </is>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>A | 4398呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>B | 4178呎 (2房)
+-
+-
+(待售)</t>
+        </is>
+      </c>
+      <c r="D7" s="19" t="inlineStr"/>
+      <c r="E7" s="19" t="inlineStr"/>
+      <c r="F7" s="19" t="inlineStr"/>
+      <c r="G7" s="19" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-铜锣湾-宏丰台10号.xlsx
+++ b/files/港岛-铜锣湾-宏丰台10号.xlsx
@@ -621,7 +621,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:N8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -634,6 +634,10 @@
     <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -691,6 +695,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -741,6 +765,26 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -791,6 +835,26 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -841,6 +905,26 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -891,6 +975,26 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L6" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -941,6 +1045,26 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L7" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -991,13 +1115,33 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="L8" s="3" t="inlineStr">
+        <is>
+          <t>暂无</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
